--- a/results/monthly_investor_report_2026-08-20.xlsx
+++ b/results/monthly_investor_report_2026-08-20.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -952,25 +952,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1343465767065309</v>
+        <v>0.134346576706531</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13434.65767065309</v>
+        <v>13434.6576706531</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>663.279323526919</v>
+        <v>663.2793235269194</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>414.7637947725073</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>374.126078049435</v>
+        <v>374.1260780494351</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9237770721826276</v>
+        <v>0.9237770721826325</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.0929986952954848</v>
+        <v>0.09299869529548477</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9299.869529548479</v>
+        <v>9299.869529548478</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0716181384209222</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>666.0393432637196</v>
+        <v>666.0393432637195</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>290.4085155120699</v>
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09214758429668768</v>
+        <v>0.09214758429668765</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9214.758429668767</v>
+        <v>9214.758429668766</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0417778692166073</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>384.9729725373314</v>
+        <v>384.9729725373313</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>39.69173522752586</v>
+        <v>39.69173522752585</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>35.84806158069362</v>
+        <v>35.84806158069361</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0.7068300883787749</v>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09106343946398338</v>
+        <v>0.09106343946398336</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9106.343946398338</v>
+        <v>9106.343946398336</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0377359140906252</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>343.6362128409725</v>
+        <v>343.6362128409724</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>93.5518942387292</v>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08944370423731328</v>
+        <v>0.08944370423731327</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8944.370423731329</v>
+        <v>8944.370423731327</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0536684495919916</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>480.0304932181254</v>
+        <v>480.0304932181253</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>423.8381338483787</v>
@@ -1235,7 +1235,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1450,7 +1450,7 @@
         <v>482.1635646835106</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>374.126078049435</v>
+        <v>374.1260780494351</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         <v>218</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.07714115080299661</v>
+        <v>-0.0771411508029967</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0299893661512347</v>
+        <v>0.0299893661512346</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.1156037188174166</v>
@@ -1555,16 +1555,16 @@
         <v>0.1107634622150022</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>35.84806158069362</v>
+        <v>35.84806158069361</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>39.69173522752586</v>
+        <v>39.69173522752585</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>42.32008621550105</v>
+        <v>42.32008621550104</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>35.84806158069362</v>
+        <v>35.84806158069361</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>0.0177083448864976</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.1124000923734837</v>
+        <v>0.1124000923734836</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>33.11816269310333</v>
@@ -1723,7 +1723,7 @@
         <v>0.0536684495919916</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.1760204477177214</v>
+        <v>0.1760204477177211</v>
       </c>
       <c r="H13" s="14" t="n">
         <v>390.9189903803491</v>
@@ -1732,7 +1732,7 @@
         <v>423.8381338483787</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>473.0542250944534</v>
+        <v>473.0542250944533</v>
       </c>
       <c r="K13" s="14" t="n">
         <v>375.5149467979344</v>
@@ -1774,7 +1774,7 @@
         <v>411</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-0.0281470913039894</v>
+        <v>-0.0281470913039895</v>
       </c>
       <c r="F14" s="18" t="n">
         <v>0.0052710954697796</v>
@@ -2002,7 +2002,7 @@
         <v>40</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>-0.0706307531256109</v>
+        <v>-0.0706307531256108</v>
       </c>
       <c r="F18" s="21" t="n">
         <v>-0.0160170779776641</v>
@@ -2011,7 +2011,7 @@
         <v>0.0525686146659375</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>37.17476987497556</v>
+        <v>37.17476987497557</v>
       </c>
       <c r="I18" s="20" t="n">
         <v>39.35931688089344</v>
@@ -2020,7 +2020,7 @@
         <v>42.1027445866375</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>37.17476987497556</v>
+        <v>37.17476987497557</v>
       </c>
       <c r="L18" s="19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2240,10 +2240,10 @@
         <v>0.2597609561752987</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.6258740850532789</v>
+        <v>0.6258740850532791</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.8525816386388203</v>
+        <v>0.8525816386388205</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>0.2368085817325154</v>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0267222289064705</v>
+        <v>0.0267222289064704</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0493707647628267</v>
@@ -2286,7 +2286,7 @@
         <v>0.1461619531956293</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.0369141594032791</v>
+        <v>0.0369141594032793</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>0.2910267401040018</v>
@@ -2300,7 +2300,7 @@
         <v>0.0197309397935816</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>0.0299893661512347</v>
+        <v>0.0299893661512346</v>
       </c>
     </row>
     <row r="6">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.098011435602196</v>
+        <v>-0.0980114356021962</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.0016017059272716</v>
+        <v>-0.0016017059272717</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.3029030422072716</v>
+        <v>0.3029030422072714</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>0.1839209653969769</v>
@@ -2415,7 +2415,7 @@
         <v>0.0112170497238826</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.1596484590301509</v>
+        <v>-0.1596484590301508</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>0.1576829052094781</v>
@@ -2498,10 +2498,10 @@
         <v>0.0281425891181987</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>0.05191756587349</v>
+        <v>0.0519175658734898</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>0.2080135694289591</v>
+        <v>0.2080135694289593</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0.0245572648966108</v>
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="E14" s="23" t="n">
-        <v>-0.0738738463805602</v>
+        <v>-0.0738738463805603</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>-0.0347417553825557</v>
+        <v>-0.0347417553825558</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>-0.1749598369930241</v>
+        <v>-0.1749598369930242</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>0.2048580599541376</v>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>-0.0720071342738285</v>
+        <v>-0.07200713427382829</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>-0.1119723751510086</v>
+        <v>-0.1119723751510085</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>0.114594639958562</v>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="J16" s="23" t="n">
-        <v>0.018762325619922</v>
+        <v>0.0187623256199221</v>
       </c>
       <c r="K16" s="23" t="n">
         <v>0.0004400050591799</v>
@@ -2799,7 +2799,7 @@
         <v>-0.0829894319240496</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>-0.1043352838645631</v>
+        <v>-0.1043352838645629</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>-0.1255961526017237</v>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="J17" s="21" t="n">
-        <v>0.0201384375410243</v>
+        <v>0.0201384375410242</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>-0.0160170779776641</v>
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>-0.0618975739687389</v>
+        <v>-0.0618975739687386</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>-0.1119116397371999</v>
+        <v>-0.1119116397371998</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>-0.2771696962838884</v>
+        <v>-0.2771696962838883</v>
       </c>
       <c r="H19" s="23" t="n">
         <v>-0.0299086319404379</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="J19" s="23" t="n">
-        <v>0.0129972957161291</v>
+        <v>0.0129972957161292</v>
       </c>
       <c r="K19" s="23" t="n">
         <v>0.0649744278262515</v>
@@ -2978,7 +2978,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3097,7 +3097,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3452,7 +3452,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3473,7 +3473,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3550,7 +3550,7 @@
         <v>4849.359929593862</v>
       </c>
       <c r="G4" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3580,7 +3580,7 @@
         <v>309813.3986530076</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3610,7 +3610,7 @@
         <v>1016118.949636504</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3640,7 +3640,7 @@
         <v>678.5705199163494</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3664,13 +3664,13 @@
         <v>38.09999847412109</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>-0.01499487658941612</v>
+        <v>-0.01499487658941623</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>-866.9169392276599</v>
+        <v>-866.9169392276672</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3700,7 +3700,7 @@
         <v>845.7754880934372</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3730,7 +3730,7 @@
         <v>6360.157754268032</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3760,7 +3760,7 @@
         <v>110.3276276744764</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>0.0505326911850554</v>

--- a/results/monthly_investor_report_2026-08-20.xlsx
+++ b/results/monthly_investor_report_2026-08-20.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1235,7 +1235,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2146,7 +2146,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2978,7 +2978,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3097,7 +3097,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3473,7 +3473,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3550,7 +3550,7 @@
         <v>4849.359929593862</v>
       </c>
       <c r="G4" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3580,7 +3580,7 @@
         <v>309813.3986530076</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3610,7 +3610,7 @@
         <v>1016118.949636504</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3640,7 +3640,7 @@
         <v>678.5705199163494</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3670,7 +3670,7 @@
         <v>-866.9169392276672</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3700,7 +3700,7 @@
         <v>845.7754880934372</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3730,7 +3730,7 @@
         <v>6360.157754268032</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3760,7 +3760,7 @@
         <v>110.3276276744764</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>0.0505326911850554</v>
